--- a/temp/lista_tecnica/originais/008_MODELO CREMALHEIRAS - OK.xlsx
+++ b/temp/lista_tecnica/originais/008_MODELO CREMALHEIRAS - OK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\FICHAS PRODUTOS MODELO IMPORTAÇÃO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\FICHAS PRODUTOS MODELO IMPORTAÇÃO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB583CC6-B180-4647-8DA9-197A4C7EBB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF14FA82-EDDF-4CAE-BD36-1CEA28FA210E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$125</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="52">
-  <si>
-    <t>GOMO 25CM P/ CREMALHEIRA PLASTICO PRETO</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="54">
   <si>
     <t>PARAFUSO PLASTIC PAN PHS 5 X 12MM ZI</t>
   </si>
@@ -193,6 +190,15 @@
   </si>
   <si>
     <t>CREMALHEIRA CHAPA 16 GOMO DE ALUMÍNIO 0,5M</t>
+  </si>
+  <si>
+    <t>GOMO 150CM P/ CREMALHEIRA PLASTICO (6X25CM) - PRETO</t>
+  </si>
+  <si>
+    <t>GOMO 100CM P/ CREMALHEIRA PLASTICO (4X25CM) - PRETO</t>
+  </si>
+  <si>
+    <t>GOMO 50CM P/ CREMALHEIRA PLASTICO (2X25CM) - PRETO</t>
   </si>
 </sst>
 </file>
@@ -1912,9 +1918,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1952,7 +1958,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2058,7 +2064,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2200,7 +2206,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2223,13 +2229,13 @@
         <v>813128</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1">
         <v>203004</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E1" s="5">
         <v>0.17299999999999999</v>
@@ -2240,13 +2246,13 @@
         <v>401162</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1">
         <v>701220</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" s="5">
         <v>1</v>
@@ -2257,13 +2263,13 @@
         <v>701220</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1">
         <v>202016</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" s="5">
         <v>2.1333333333333E-3</v>
@@ -2274,13 +2280,13 @@
         <v>813101</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1">
         <v>105008</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="5">
         <v>2.1000000000000001E-2</v>
@@ -2291,13 +2297,13 @@
         <v>813129</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1">
         <v>105008</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5" s="5">
         <v>2.1000000000000001E-2</v>
@@ -2308,13 +2314,13 @@
         <v>813375</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1">
         <v>201073</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" s="5">
         <v>0.79800000000000004</v>
@@ -2325,13 +2331,13 @@
         <v>813525</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1">
         <v>201134</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" s="5">
         <v>0.184</v>
@@ -2342,13 +2348,13 @@
         <v>2001015</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1">
         <v>813146</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5">
         <v>6</v>
@@ -2359,13 +2365,13 @@
         <v>2001015</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1">
         <v>401007</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" s="5">
         <v>18</v>
@@ -2376,13 +2382,13 @@
         <v>2001015</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1">
         <v>201066</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="5">
         <v>0.63100000000000001</v>
@@ -2393,13 +2399,13 @@
         <v>2001015</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1">
         <v>105008</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" s="5">
         <v>2.1000000000000001E-2</v>
@@ -2410,13 +2416,13 @@
         <v>2001016</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1">
         <v>813146</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5">
         <v>4</v>
@@ -2427,13 +2433,13 @@
         <v>2001016</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1">
         <v>401007</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="5">
         <v>12</v>
@@ -2444,13 +2450,13 @@
         <v>2001016</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1">
         <v>201066</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5">
         <v>0.42399999999999999</v>
@@ -2461,13 +2467,13 @@
         <v>2001016</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
         <v>105008</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" s="5">
         <v>2.1000000000000001E-2</v>
@@ -2478,16 +2484,16 @@
         <v>2001018</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1">
-        <v>813080</v>
+        <v>401163</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>0</v>
       </c>
       <c r="E16" s="5">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -2495,16 +2501,16 @@
         <v>2001018</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1">
-        <v>401163</v>
+        <v>201066</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E17" s="5">
-        <v>18</v>
+        <v>0.63100000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -2512,33 +2518,33 @@
         <v>2001018</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1">
-        <v>201066</v>
+        <v>105008</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E18" s="5">
-        <v>0.63100000000000001</v>
+        <v>2.2200000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
-        <v>2001018</v>
+        <v>2001019</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="1">
-        <v>105008</v>
+        <v>401163</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E19" s="5">
-        <v>2.2200000000000001E-2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -2546,16 +2552,16 @@
         <v>2001019</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="1">
-        <v>813080</v>
+        <v>201066</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="5">
-        <v>4</v>
+        <v>0.42399999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -2563,50 +2569,50 @@
         <v>2001019</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1">
-        <v>401163</v>
+        <v>105008</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E21" s="5">
-        <v>12</v>
+        <v>2.2200000000000001E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
-        <v>2001019</v>
+        <v>2001021</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="1">
-        <v>201066</v>
+        <v>401163</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="5">
-        <v>0.42399999999999999</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
-        <v>2001019</v>
+        <v>2001021</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="1">
-        <v>105008</v>
+        <v>201072</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E23" s="5">
-        <v>2.2200000000000001E-2</v>
+        <v>0.38100000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -2614,21 +2620,21 @@
         <v>2001021</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="1">
-        <v>813080</v>
+        <v>105008</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E24" s="5">
-        <v>4</v>
+        <v>2.2200000000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
-        <v>2001021</v>
+        <v>2001022</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>8</v>
@@ -2637,15 +2643,15 @@
         <v>401163</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
-        <v>2001021</v>
+        <v>2001022</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>8</v>
@@ -2654,15 +2660,15 @@
         <v>201072</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E26" s="5">
-        <v>0.38100000000000001</v>
+        <v>0.57150000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
-        <v>2001021</v>
+        <v>2001022</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>8</v>
@@ -2671,7 +2677,7 @@
         <v>105008</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" s="5">
         <v>2.2200000000000001E-2</v>
@@ -2679,13 +2685,13 @@
     </row>
     <row r="28" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
-        <v>2001022</v>
+        <v>2001023</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="1">
-        <v>813080</v>
+        <v>401163</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>0</v>
@@ -2696,1240 +2702,1240 @@
     </row>
     <row r="29" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
-        <v>2001022</v>
+        <v>2001023</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="1">
-        <v>401163</v>
+        <v>201066</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E29" s="5">
-        <v>18</v>
+        <v>0.21199999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
-        <v>2001022</v>
+        <v>2001023</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="1">
-        <v>201072</v>
+        <v>105008</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E30" s="5">
-        <v>0.57150000000000001</v>
+        <v>6.1999999999999998E-3</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
-        <v>2001022</v>
+        <v>2001028</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" s="1">
-        <v>105008</v>
+        <v>813146</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5">
-        <v>2.2200000000000001E-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
-        <v>2001023</v>
+        <v>2001028</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="1">
-        <v>813080</v>
+        <v>401007</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E32" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
-        <v>2001023</v>
+        <v>2001028</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="1">
-        <v>401163</v>
+        <v>201066</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E33" s="5">
-        <v>6</v>
+        <v>0.21199999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
-        <v>2001023</v>
+        <v>2001028</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="1">
-        <v>201066</v>
+        <v>105008</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E34" s="5">
-        <v>0.21199999999999999</v>
+        <v>6.1999999999999998E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
-        <v>2001023</v>
+        <v>2001044</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="1">
-        <v>105008</v>
+        <v>401163</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E35" s="5">
-        <v>6.1999999999999998E-3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
-        <v>2001028</v>
+        <v>2001044</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="1">
-        <v>813146</v>
+        <v>201066</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" s="5">
-        <v>2</v>
+        <v>0.21199999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
-        <v>2001028</v>
+        <v>2001044</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="1">
-        <v>401007</v>
+        <v>105008</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E37" s="5">
-        <v>6</v>
+        <v>6.1999999999999998E-3</v>
       </c>
     </row>
     <row r="38" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
-        <v>2001028</v>
+        <v>2001045</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C38" s="1">
-        <v>201066</v>
+        <v>813084</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E38" s="5">
-        <v>0.21199999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
-        <v>2001028</v>
+        <v>2001045</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C39" s="1">
         <v>105008</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E39" s="5">
-        <v>6.1999999999999998E-3</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
-        <v>2001044</v>
+        <v>2001046</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C40" s="1">
-        <v>813080</v>
+        <v>401163</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>0</v>
       </c>
       <c r="E40" s="5">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
-        <v>2001044</v>
+        <v>2001046</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41" s="1">
-        <v>401163</v>
+        <v>201072</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E41" s="5">
-        <v>6</v>
+        <v>0.57150000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
-        <v>2001044</v>
+        <v>2001046</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42" s="1">
-        <v>201066</v>
+        <v>105008</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E42" s="5">
-        <v>0.21199999999999999</v>
+        <v>2.2200000000000001E-2</v>
       </c>
     </row>
     <row r="43" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
-        <v>2001044</v>
+        <v>2001134</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C43" s="1">
-        <v>105008</v>
+        <v>813146</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E43" s="5">
-        <v>6.1999999999999998E-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
-        <v>2001045</v>
+        <v>2001134</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C44" s="1">
-        <v>813084</v>
+        <v>401007</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E44" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="9">
+        <v>2001134</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="1">
+        <v>201066</v>
+      </c>
+      <c r="D45" s="10" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A45" s="9">
-        <v>2001045</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="1">
-        <v>105008</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>48</v>
-      </c>
       <c r="E45" s="5">
-        <v>2.1000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+        <v>0.21199999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
-        <v>2001046</v>
+        <v>2001134</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C46" s="1">
-        <v>813080</v>
+        <v>105008</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E46" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+        <v>6.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
-        <v>2001046</v>
+        <v>2001135</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C47" s="1">
         <v>401163</v>
       </c>
       <c r="D47" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="9">
+        <v>2001135</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="1">
+        <v>201066</v>
+      </c>
+      <c r="D48" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E47" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A48" s="9">
-        <v>2001046</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" s="1">
-        <v>201072</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="E48" s="5">
-        <v>0.57150000000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+        <v>0.42399999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
-        <v>2001046</v>
+        <v>2001135</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C49" s="1">
         <v>105008</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E49" s="5">
         <v>2.2200000000000001E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
-        <v>2001134</v>
+        <v>2001136</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C50" s="1">
-        <v>813146</v>
+        <v>401163</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E50" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
-        <v>2001134</v>
+        <v>2001136</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="1">
-        <v>401007</v>
+        <v>201066</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E51" s="5">
-        <v>6</v>
+        <v>0.63100000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
-        <v>2001134</v>
+        <v>2001136</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C52" s="1">
-        <v>201066</v>
+        <v>105008</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E52" s="5">
-        <v>0.21199999999999999</v>
+        <v>2.2200000000000001E-2</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
-        <v>2001134</v>
+        <v>2001137</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C53" s="1">
-        <v>105008</v>
+        <v>813146</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E53" s="5">
-        <v>6.1999999999999998E-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
-        <v>2001135</v>
+        <v>2001137</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1">
-        <v>813080</v>
+        <v>401007</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E54" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
-        <v>2001135</v>
+        <v>2001137</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C55" s="1">
-        <v>401163</v>
+        <v>201066</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E55" s="5">
-        <v>12</v>
+        <v>0.42399999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
-        <v>2001135</v>
+        <v>2001137</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1">
-        <v>201066</v>
+        <v>105008</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E56" s="5">
-        <v>0.42399999999999999</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
-        <v>2001135</v>
+        <v>2001228</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C57" s="1">
-        <v>105008</v>
+        <v>813146</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E57" s="5">
-        <v>2.2200000000000001E-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
-        <v>2001136</v>
+        <v>2001228</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C58" s="1">
-        <v>813080</v>
+        <v>401007</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E58" s="5">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
-        <v>2001136</v>
+        <v>2001228</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1">
-        <v>401163</v>
+        <v>201066</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E59" s="5">
-        <v>18</v>
+        <v>0.63100000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
-        <v>2001136</v>
+        <v>2001228</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C60" s="1">
-        <v>201066</v>
+        <v>105008</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E60" s="5">
-        <v>0.63100000000000001</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
-        <v>2001136</v>
+        <v>2001232</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C61" s="1">
-        <v>105008</v>
+        <v>401163</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E61" s="5">
-        <v>2.2200000000000001E-2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
-        <v>2001137</v>
+        <v>2001232</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C62" s="1">
-        <v>813146</v>
+        <v>201072</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E62" s="5">
-        <v>4</v>
+        <v>0.38100000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
-        <v>2001137</v>
+        <v>2001232</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63" s="1">
-        <v>401007</v>
+        <v>105008</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E63" s="5">
-        <v>12</v>
+        <v>2.2200000000000001E-2</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
-        <v>2001137</v>
+        <v>2004028</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C64" s="1">
-        <v>201066</v>
+        <v>813146</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E64" s="5">
-        <v>0.42399999999999999</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
-        <v>2001137</v>
+        <v>2004028</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C65" s="1">
-        <v>105008</v>
+        <v>401007</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E65" s="5">
-        <v>2.1000000000000001E-2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
-        <v>2001228</v>
+        <v>2004028</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C66" s="1">
-        <v>813146</v>
+        <v>201066</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E66" s="5">
-        <v>6</v>
+        <v>0.42399999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
-        <v>2001228</v>
+        <v>2004028</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C67" s="1">
-        <v>401007</v>
+        <v>105008</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E67" s="5">
-        <v>18</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
-        <v>2001228</v>
+        <v>2004046</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C68" s="1">
-        <v>201066</v>
+        <v>401163</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E68" s="5">
-        <v>0.63100000000000001</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
-        <v>2001228</v>
+        <v>2004046</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C69" s="1">
-        <v>105008</v>
+        <v>201066</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E69" s="5">
-        <v>2.1000000000000001E-2</v>
+        <v>0.42399999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
-        <v>2001232</v>
+        <v>2004046</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C70" s="1">
-        <v>813080</v>
+        <v>811276</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E70" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
-        <v>2001232</v>
+        <v>2004046</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C71" s="1">
-        <v>401163</v>
+        <v>105008</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E71" s="5">
-        <v>12</v>
+        <v>2.2200000000000001E-2</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
-        <v>2001232</v>
+        <v>2004058</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C72" s="1">
-        <v>201072</v>
+        <v>813146</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E72" s="5">
-        <v>0.38100000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
-        <v>2001232</v>
+        <v>2004058</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C73" s="1">
-        <v>105008</v>
+        <v>401007</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E73" s="5">
-        <v>2.2200000000000001E-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
-        <v>2004028</v>
+        <v>2004058</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C74" s="1">
-        <v>813146</v>
+        <v>201066</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E74" s="5">
-        <v>4</v>
+        <v>0.21199999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
-        <v>2004028</v>
+        <v>2004058</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C75" s="1">
-        <v>401007</v>
+        <v>105008</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E75" s="5">
-        <v>12</v>
+        <v>6.1999999999999998E-3</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
-        <v>2004028</v>
+        <v>2004059</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C76" s="1">
-        <v>201066</v>
+        <v>401163</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E76" s="5">
-        <v>0.42399999999999999</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
-        <v>2004028</v>
+        <v>2004059</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C77" s="1">
-        <v>105008</v>
+        <v>201066</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E77" s="5">
-        <v>2.1000000000000001E-2</v>
+        <v>0.21199999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
-        <v>2004046</v>
+        <v>2004059</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C78" s="1">
-        <v>813080</v>
+        <v>105008</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E78" s="5">
-        <v>4</v>
+        <v>6.1999999999999998E-3</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
-        <v>2004046</v>
+        <v>2004060</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C79" s="1">
-        <v>401163</v>
+        <v>813146</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E79" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
-        <v>2004046</v>
+        <v>2004060</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C80" s="1">
-        <v>201066</v>
+        <v>401007</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E80" s="5">
-        <v>0.42399999999999999</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
-        <v>2004046</v>
+        <v>2004060</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C81" s="1">
-        <v>811276</v>
+        <v>201066</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E81" s="5">
-        <v>1</v>
+        <v>0.63100000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
-        <v>2004046</v>
+        <v>2004060</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C82" s="1">
-        <v>105008</v>
+        <v>811276</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E82" s="5">
-        <v>2.2200000000000001E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
-        <v>2004058</v>
+        <v>2004060</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C83" s="1">
-        <v>813146</v>
+        <v>105008</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="E83" s="5">
-        <v>2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
-        <v>2004058</v>
+        <v>2004061</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C84" s="1">
-        <v>401007</v>
+        <v>401163</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E84" s="5">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
-        <v>2004058</v>
+        <v>2004061</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C85" s="1">
         <v>201066</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" s="5">
-        <v>0.21199999999999999</v>
+        <v>0.63100000000000001</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
-        <v>2004058</v>
+        <v>2004061</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C86" s="1">
-        <v>105008</v>
+        <v>811276</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E86" s="5">
-        <v>6.1999999999999998E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
-        <v>2004059</v>
+        <v>2004061</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C87" s="1">
-        <v>813080</v>
+        <v>105008</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E87" s="5">
-        <v>2</v>
+        <v>2.2200000000000001E-2</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
-        <v>2004059</v>
+        <v>2010153</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C88" s="1">
-        <v>401163</v>
+        <v>813146</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
-        <v>2004059</v>
+        <v>2010153</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C89" s="1">
-        <v>201066</v>
+        <v>401007</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E89" s="5">
-        <v>0.21199999999999999</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
-        <v>2004059</v>
+        <v>2010153</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C90" s="1">
-        <v>105008</v>
+        <v>201066</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E90" s="5">
-        <v>6.1999999999999998E-3</v>
+        <v>0.42399999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
-        <v>2004060</v>
+        <v>2010153</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C91" s="1">
-        <v>813146</v>
+        <v>105008</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="E91" s="5">
-        <v>6</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
-        <v>2004060</v>
+        <v>2010154</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C92" s="1">
-        <v>401007</v>
+        <v>401163</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E92" s="5">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
-        <v>2004060</v>
+        <v>2010154</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C93" s="1">
         <v>201066</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" s="5">
-        <v>0.63100000000000001</v>
+        <v>0.42399999999999999</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
-        <v>2004060</v>
+        <v>2010226</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C94" s="1">
-        <v>811276</v>
+        <v>813127</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E94" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
-        <v>2004060</v>
+        <v>2010226</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C95" s="1">
-        <v>105008</v>
+        <v>401163</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E95" s="5">
-        <v>2.1000000000000001E-2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
-        <v>2004061</v>
+        <v>2010226</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C96" s="1">
-        <v>813080</v>
+        <v>813375</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E96" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
-        <v>2004061</v>
+        <v>2010229</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C97" s="1">
-        <v>401163</v>
+        <v>813146</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E97" s="5">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
-        <v>2004061</v>
+        <v>2010229</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C98" s="1">
-        <v>201066</v>
+        <v>401007</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E98" s="5">
-        <v>0.63100000000000001</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
-        <v>2004061</v>
+        <v>2010229</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C99" s="1">
-        <v>811276</v>
+        <v>201066</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E99" s="5">
-        <v>1</v>
+        <v>0.42399999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
-        <v>2004061</v>
+        <v>2010229</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C100" s="1">
         <v>105008</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E100" s="5">
-        <v>2.2200000000000001E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
-        <v>2010153</v>
+        <v>2010324</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C101" s="1">
-        <v>813146</v>
+        <v>813128</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="E101" s="5">
         <v>4</v>
@@ -3937,16 +3943,16 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
-        <v>2010153</v>
+        <v>2010324</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C102" s="1">
         <v>401007</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E102" s="5">
         <v>12</v>
@@ -3954,636 +3960,636 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
-        <v>2010153</v>
+        <v>2010324</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C103" s="1">
-        <v>201066</v>
+        <v>813375</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E103" s="5">
-        <v>0.42399999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
-        <v>2010153</v>
+        <v>2010325</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C104" s="1">
-        <v>105008</v>
+        <v>813128</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E104" s="5">
-        <v>2.1000000000000001E-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
-        <v>2010154</v>
+        <v>2010325</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C105" s="1">
-        <v>813080</v>
+        <v>401007</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E105" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
-        <v>2010154</v>
+        <v>2010325</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C106" s="1">
-        <v>401163</v>
+        <v>813375</v>
       </c>
       <c r="D106" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E106" s="5">
         <v>1</v>
-      </c>
-      <c r="E106" s="5">
-        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
-        <v>2010154</v>
+        <v>2010328</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C107" s="1">
-        <v>201066</v>
+        <v>813128</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E107" s="5">
-        <v>0.42399999999999999</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
-        <v>2010226</v>
+        <v>2010328</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C108" s="1">
-        <v>813127</v>
+        <v>401007</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E108" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
-        <v>2010226</v>
+        <v>2010328</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C109" s="1">
-        <v>401163</v>
+        <v>813375</v>
       </c>
       <c r="D109" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E109" s="5">
         <v>1</v>
-      </c>
-      <c r="E109" s="5">
-        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
-        <v>2010226</v>
+        <v>813084</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C110" s="1">
-        <v>813375</v>
+        <v>813146</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E110" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
-        <v>2010229</v>
+        <v>813084</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C111" s="1">
-        <v>813146</v>
+        <v>401007</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="E111" s="5">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
-        <v>2010229</v>
+        <v>813084</v>
       </c>
       <c r="B112" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" s="1">
+        <v>201072</v>
+      </c>
+      <c r="D112" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C112" s="1">
-        <v>401007</v>
-      </c>
-      <c r="D112" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="E112" s="5">
-        <v>12</v>
+        <v>0.57150000000000001</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="9">
-        <v>2010229</v>
+        <v>813084</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C113" s="1">
+        <v>105008</v>
+      </c>
+      <c r="D113" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E113" s="5">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>813101</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C114" s="1">
+        <v>813146</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E114" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>813101</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C115" s="1">
+        <v>401007</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>813101</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C116" s="1">
         <v>201066</v>
       </c>
-      <c r="D113" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E113" s="5">
-        <v>0.42399999999999999</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="9">
-        <v>2010229</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C114" s="1">
+      <c r="D116" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E116" s="5">
+        <v>0.63100000000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>813129</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C117" s="1">
+        <v>813146</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E117" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>813129</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C118" s="1">
+        <v>401007</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>813129</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C119" s="1">
+        <v>201066</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E119" s="5">
+        <v>0.63100000000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>813126</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C120" s="1">
         <v>105008</v>
       </c>
-      <c r="D114" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E114" s="5">
+      <c r="D120" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E120" s="5">
+        <v>6.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>2010154</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C121" s="1">
+        <v>105008</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E121" s="5">
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="9">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>2010226</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C122" s="1">
+        <v>105008</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E122" s="5">
+        <v>2.7120000000000002</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
         <v>2010324</v>
       </c>
-      <c r="B115" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C115" s="1">
-        <v>813128</v>
-      </c>
-      <c r="D115" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E115" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="9">
-        <v>2010324</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C116" s="1">
-        <v>401007</v>
-      </c>
-      <c r="D116" s="10" t="s">
+      <c r="B123" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C123" s="1">
+        <v>105008</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E123" s="5">
+        <v>2.7120000000000002</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>2010325</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E116" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="9">
-        <v>2010324</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C117" s="1">
-        <v>813375</v>
-      </c>
-      <c r="D117" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E117" s="5">
+      <c r="C124" s="1">
+        <v>105008</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E124" s="5">
+        <v>2.7120000000000002</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>2010328</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C125" s="1">
+        <v>105008</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E125" s="5">
+        <v>2.7120000000000002</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>2001018</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" s="1">
+        <v>813629</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E126" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="9">
-        <v>2010325</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C118" s="1">
-        <v>813128</v>
-      </c>
-      <c r="D118" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E118" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="9">
-        <v>2010325</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C119" s="1">
-        <v>401007</v>
-      </c>
-      <c r="D119" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E119" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="9">
-        <v>2010325</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C120" s="1">
-        <v>813375</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E120" s="5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <v>2001019</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="1">
+        <v>813628</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E127" s="5">
         <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="9">
-        <v>2010328</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C121" s="1">
-        <v>813128</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E121" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="9">
-        <v>2010328</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C122" s="1">
-        <v>401007</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E122" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="9">
-        <v>2010328</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C123" s="1">
-        <v>813375</v>
-      </c>
-      <c r="D123" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E123" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="9">
-        <v>813084</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C124" s="1">
-        <v>813146</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E124" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="9">
-        <v>813084</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C125" s="1">
-        <v>401007</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E125" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="9">
-        <v>813084</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C126" s="1">
-        <v>201072</v>
-      </c>
-      <c r="D126" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E126" s="5">
-        <v>0.57150000000000001</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="9">
-        <v>813084</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C127" s="1">
-        <v>105008</v>
-      </c>
-      <c r="D127" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E127" s="5">
-        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>813101</v>
+        <v>2001021</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C128" s="2">
-        <v>813146</v>
+        <v>7</v>
+      </c>
+      <c r="C128" s="1">
+        <v>813628</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="E128" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>813101</v>
+        <v>2001022</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C129" s="2">
-        <v>401007</v>
+        <v>8</v>
+      </c>
+      <c r="C129" s="1">
+        <v>813629</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E129" s="5">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
-        <v>813101</v>
+        <v>2001023</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C130" s="2">
-        <v>201066</v>
+        <v>9</v>
+      </c>
+      <c r="C130" s="1">
+        <v>813627</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="E130" s="5">
-        <v>0.63100000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
-        <v>813129</v>
+        <v>2001044</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C131" s="2">
-        <v>813146</v>
+        <v>11</v>
+      </c>
+      <c r="C131" s="1">
+        <v>813627</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E131" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
-        <v>813129</v>
+        <v>2001046</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C132" s="2">
-        <v>401007</v>
+        <v>13</v>
+      </c>
+      <c r="C132" s="1">
+        <v>813629</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E132" s="5">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
-        <v>813129</v>
+        <v>2001135</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C133" s="2">
-        <v>201066</v>
+        <v>15</v>
+      </c>
+      <c r="C133" s="1">
+        <v>813628</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="E133" s="5">
-        <v>0.63100000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>813126</v>
+        <v>2001136</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" s="1">
+        <v>813629</v>
+      </c>
+      <c r="D134" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C134" s="2">
-        <v>105008</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="E134" s="5">
-        <v>6.1999999999999998E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
-        <v>2010154</v>
+        <v>2001232</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C135" s="2">
-        <v>105008</v>
+        <v>19</v>
+      </c>
+      <c r="C135" s="1">
+        <v>813628</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E135" s="5">
-        <v>2.1000000000000001E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>2010226</v>
+        <v>2004046</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C136" s="2">
-        <v>105008</v>
+        <v>21</v>
+      </c>
+      <c r="C136" s="1">
+        <v>813628</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E136" s="5">
-        <v>2.7120000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
-        <v>2010324</v>
+        <v>2004059</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C137" s="2">
-        <v>105008</v>
+        <v>23</v>
+      </c>
+      <c r="C137" s="1">
+        <v>813627</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E137" s="5">
-        <v>2.7120000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
-        <v>2010325</v>
+        <v>2004061</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C138" s="2">
-        <v>105008</v>
+        <v>25</v>
+      </c>
+      <c r="C138" s="1">
+        <v>813629</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E138" s="5">
-        <v>2.7120000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>2010328</v>
+        <v>2010154</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C139" s="2">
-        <v>105008</v>
+        <v>27</v>
+      </c>
+      <c r="C139" s="1">
+        <v>813628</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E139" s="5">
-        <v>2.7120000000000002</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E127" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E127">
+  <autoFilter ref="A1:E125" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E113">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
